--- a/data/nzd0602/nzd0602.xlsx
+++ b/data/nzd0602/nzd0602.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M390"/>
+  <dimension ref="A1:M393"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18000,6 +18000,141 @@
       <c r="M390" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:29+00:00</t>
+        </is>
+      </c>
+      <c r="B391" t="n">
+        <v>204</v>
+      </c>
+      <c r="C391" t="n">
+        <v>190.84</v>
+      </c>
+      <c r="D391" t="n">
+        <v>197.66</v>
+      </c>
+      <c r="E391" t="n">
+        <v>207.03</v>
+      </c>
+      <c r="F391" t="n">
+        <v>202.63</v>
+      </c>
+      <c r="G391" t="n">
+        <v>208.15</v>
+      </c>
+      <c r="H391" t="n">
+        <v>209.37</v>
+      </c>
+      <c r="I391" t="n">
+        <v>213.65</v>
+      </c>
+      <c r="J391" t="n">
+        <v>209.4</v>
+      </c>
+      <c r="K391" t="n">
+        <v>212.32</v>
+      </c>
+      <c r="L391" t="n">
+        <v>209.71</v>
+      </c>
+      <c r="M391" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B392" t="n">
+        <v>204.7</v>
+      </c>
+      <c r="C392" t="n">
+        <v>193.5</v>
+      </c>
+      <c r="D392" t="n">
+        <v>199.49</v>
+      </c>
+      <c r="E392" t="n">
+        <v>209.68</v>
+      </c>
+      <c r="F392" t="n">
+        <v>204.52</v>
+      </c>
+      <c r="G392" t="n">
+        <v>211.09</v>
+      </c>
+      <c r="H392" t="n">
+        <v>210.34</v>
+      </c>
+      <c r="I392" t="n">
+        <v>213.78</v>
+      </c>
+      <c r="J392" t="n">
+        <v>210.77</v>
+      </c>
+      <c r="K392" t="n">
+        <v>212.52</v>
+      </c>
+      <c r="L392" t="n">
+        <v>209.64</v>
+      </c>
+      <c r="M392" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B393" t="n">
+        <v>204.44</v>
+      </c>
+      <c r="C393" t="n">
+        <v>192.94</v>
+      </c>
+      <c r="D393" t="n">
+        <v>198.88</v>
+      </c>
+      <c r="E393" t="n">
+        <v>209.01</v>
+      </c>
+      <c r="F393" t="n">
+        <v>204.3</v>
+      </c>
+      <c r="G393" t="n">
+        <v>210.54</v>
+      </c>
+      <c r="H393" t="n">
+        <v>210.38</v>
+      </c>
+      <c r="I393" t="n">
+        <v>213.96</v>
+      </c>
+      <c r="J393" t="n">
+        <v>211.58</v>
+      </c>
+      <c r="K393" t="n">
+        <v>212.61</v>
+      </c>
+      <c r="L393" t="n">
+        <v>209.31</v>
+      </c>
+      <c r="M393" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -18014,7 +18149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B420"/>
+  <dimension ref="A1:B423"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22217,6 +22352,36 @@
       </c>
       <c r="B420" t="n">
         <v>1.38</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B421" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B422" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B423" t="n">
+        <v>0.43</v>
       </c>
     </row>
   </sheetData>
@@ -22379,28 +22544,28 @@
         <v>0.1008</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0121996156404694</v>
+        <v>-0.007101249086859079</v>
       </c>
       <c r="J2" t="n">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="K2" t="n">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0004864653921223816</v>
+        <v>0.000166547564556363</v>
       </c>
       <c r="M2" t="n">
-        <v>3.272058607844716</v>
+        <v>3.271313522953939</v>
       </c>
       <c r="N2" t="n">
-        <v>15.81200326319806</v>
+        <v>15.77787976782465</v>
       </c>
       <c r="O2" t="n">
-        <v>3.976430970505846</v>
+        <v>3.972137934138825</v>
       </c>
       <c r="P2" t="n">
-        <v>201.307916216816</v>
+        <v>201.2502370382308</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22451,28 +22616,28 @@
         <v>0.0982</v>
       </c>
       <c r="I3" t="n">
-        <v>0.07208394351000064</v>
+        <v>0.07704559605617409</v>
       </c>
       <c r="J3" t="n">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="K3" t="n">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02525573544563831</v>
+        <v>0.0289369534789794</v>
       </c>
       <c r="M3" t="n">
-        <v>2.630286143137462</v>
+        <v>2.635197094557477</v>
       </c>
       <c r="N3" t="n">
-        <v>10.36968617536686</v>
+        <v>10.38197628850601</v>
       </c>
       <c r="O3" t="n">
-        <v>3.220199710478662</v>
+        <v>3.222107429696597</v>
       </c>
       <c r="P3" t="n">
-        <v>187.2012543052224</v>
+        <v>187.1451126938369</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22523,28 +22688,28 @@
         <v>0.0887</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.002157445833716302</v>
+        <v>0.006105822735555167</v>
       </c>
       <c r="J4" t="n">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="K4" t="n">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="L4" t="n">
-        <v>2.198076319626097e-05</v>
+        <v>0.0001750734338057391</v>
       </c>
       <c r="M4" t="n">
-        <v>2.618869527748166</v>
+        <v>2.641153481603148</v>
       </c>
       <c r="N4" t="n">
-        <v>10.94927483613112</v>
+        <v>11.09639392441174</v>
       </c>
       <c r="O4" t="n">
-        <v>3.308968847863504</v>
+        <v>3.3311250238338</v>
       </c>
       <c r="P4" t="n">
-        <v>193.2325621027854</v>
+        <v>193.1390747916059</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22595,28 +22760,28 @@
         <v>0.115</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.03492396083454365</v>
+        <v>-0.03244782917268845</v>
       </c>
       <c r="J5" t="n">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="K5" t="n">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004779113646533273</v>
+        <v>0.004183135173913777</v>
       </c>
       <c r="M5" t="n">
-        <v>2.910673481384913</v>
+        <v>2.902582621200208</v>
       </c>
       <c r="N5" t="n">
-        <v>13.13339414127574</v>
+        <v>13.06287119992319</v>
       </c>
       <c r="O5" t="n">
-        <v>3.624002502934531</v>
+        <v>3.61425942620659</v>
       </c>
       <c r="P5" t="n">
-        <v>207.8544253539701</v>
+        <v>207.8264025549225</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22667,28 +22832,28 @@
         <v>0.098</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1364674441875046</v>
+        <v>-0.1340078796300126</v>
       </c>
       <c r="J6" t="n">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="K6" t="n">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05295069957028564</v>
+        <v>0.05184443332004873</v>
       </c>
       <c r="M6" t="n">
-        <v>3.132128295218902</v>
+        <v>3.120471578016537</v>
       </c>
       <c r="N6" t="n">
-        <v>17.22331999505287</v>
+        <v>17.11701025382853</v>
       </c>
       <c r="O6" t="n">
-        <v>4.150098793408763</v>
+        <v>4.137270870251128</v>
       </c>
       <c r="P6" t="n">
-        <v>205.8132419690635</v>
+        <v>205.7854082886201</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -22739,28 +22904,28 @@
         <v>0.1269</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1637270331478027</v>
+        <v>-0.1559404103085435</v>
       </c>
       <c r="J7" t="n">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="K7" t="n">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="L7" t="n">
-        <v>0.09146491548190216</v>
+        <v>0.08368856316305362</v>
       </c>
       <c r="M7" t="n">
-        <v>3.100666945506437</v>
+        <v>3.11563036574475</v>
       </c>
       <c r="N7" t="n">
-        <v>13.76847432366579</v>
+        <v>13.87663334348247</v>
       </c>
       <c r="O7" t="n">
-        <v>3.710589484659519</v>
+        <v>3.725135345659601</v>
       </c>
       <c r="P7" t="n">
-        <v>209.1040861361526</v>
+        <v>209.0159845797809</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -22811,28 +22976,28 @@
         <v>0.1724</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0795851689561578</v>
+        <v>-0.07525624520114552</v>
       </c>
       <c r="J8" t="n">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="K8" t="n">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03534367994515875</v>
+        <v>0.0319814602016133</v>
       </c>
       <c r="M8" t="n">
-        <v>2.419826395017451</v>
+        <v>2.422864551938335</v>
       </c>
       <c r="N8" t="n">
-        <v>8.938877847445145</v>
+        <v>8.934294231278228</v>
       </c>
       <c r="O8" t="n">
-        <v>2.989795619677898</v>
+        <v>2.98902897799239</v>
       </c>
       <c r="P8" t="n">
-        <v>209.2649042860688</v>
+        <v>209.2159265413962</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -22883,28 +23048,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2512814975030029</v>
+        <v>0.2566666165774941</v>
       </c>
       <c r="J9" t="n">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="K9" t="n">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2032158615949112</v>
+        <v>0.2115052235993591</v>
       </c>
       <c r="M9" t="n">
-        <v>2.784642012119576</v>
+        <v>2.790100254837131</v>
       </c>
       <c r="N9" t="n">
-        <v>12.80153268429339</v>
+        <v>12.79989086301746</v>
       </c>
       <c r="O9" t="n">
-        <v>3.577922956729699</v>
+        <v>3.577693511610163</v>
       </c>
       <c r="P9" t="n">
-        <v>203.512674618035</v>
+        <v>203.4517522436658</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -22955,28 +23120,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3712073748353832</v>
+        <v>0.3672758248711815</v>
       </c>
       <c r="J10" t="n">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="K10" t="n">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4272151879589954</v>
+        <v>0.4243421659111853</v>
       </c>
       <c r="M10" t="n">
-        <v>2.56950595712034</v>
+        <v>2.56803242843679</v>
       </c>
       <c r="N10" t="n">
-        <v>9.552914056117414</v>
+        <v>9.537239495663828</v>
       </c>
       <c r="O10" t="n">
-        <v>3.090778875318876</v>
+        <v>3.088242136825386</v>
       </c>
       <c r="P10" t="n">
-        <v>203.3150935552467</v>
+        <v>203.3595585661643</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -23027,28 +23192,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4058311725575162</v>
+        <v>0.4040760918189107</v>
       </c>
       <c r="J11" t="n">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="K11" t="n">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5378604651065038</v>
+        <v>0.5392262294349209</v>
       </c>
       <c r="M11" t="n">
-        <v>2.036931492845067</v>
+        <v>2.030887823404288</v>
       </c>
       <c r="N11" t="n">
-        <v>7.317322135569198</v>
+        <v>7.271647573920106</v>
       </c>
       <c r="O11" t="n">
-        <v>2.705054922837833</v>
+        <v>2.696599260906245</v>
       </c>
       <c r="P11" t="n">
-        <v>202.8423954613835</v>
+        <v>202.8622488265618</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -23099,28 +23264,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3435231708225568</v>
+        <v>0.3389256616325262</v>
       </c>
       <c r="J12" t="n">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="K12" t="n">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3969578265492979</v>
+        <v>0.3924223669866008</v>
       </c>
       <c r="M12" t="n">
-        <v>2.333126078310286</v>
+        <v>2.334005154729851</v>
       </c>
       <c r="N12" t="n">
-        <v>9.2698617471447</v>
+        <v>9.269294960197398</v>
       </c>
       <c r="O12" t="n">
-        <v>3.044644765345327</v>
+        <v>3.044551684599458</v>
       </c>
       <c r="P12" t="n">
-        <v>203.4688149278407</v>
+        <v>203.5208278885988</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -23158,7 +23323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M390"/>
+  <dimension ref="A1:M393"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49291,6 +49456,207 @@
         </is>
       </c>
     </row>
+    <row r="391">
+      <c r="A391" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:29+00:00</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>-36.87899240317589,175.04223386085047</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>-36.8795469807017,175.04282587356013</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>-36.87996370731912,175.04356205432126</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>-36.88030882249866,175.04433647608374</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>-36.88065614263891,175.04512433482245</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>-36.88085051132959,175.04597262094404</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>-36.88101175340142,175.04684725548677</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>-36.88103221067041,175.04771988738975</t>
+        </is>
+      </c>
+      <c r="J391" t="inlineStr">
+        <is>
+          <t>-36.881101225800755,175.04861438185256</t>
+        </is>
+      </c>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>-36.881050804099814,175.04949936605286</t>
+        </is>
+      </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>-36.88100295721487,175.05037692417588</t>
+        </is>
+      </c>
+      <c r="M391" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>-36.87898757373101,175.04223891149718</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>-36.87952862871607,175.0428450660005</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>-36.879951081625755,175.04357525808737</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>-36.880287292036904,175.04434933095726</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>-36.88064078689481,175.04513350289344</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>-36.88082478729238,175.04598050418107</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>-36.88100326432717,175.04684984682243</t>
+        </is>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>-36.8810310403272,175.04771994985703</t>
+        </is>
+      </c>
+      <c r="J392" t="inlineStr">
+        <is>
+          <t>-36.881088892183286,175.04861504001735</t>
+        </is>
+      </c>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>-36.88104900411832,175.04949925524681</t>
+        </is>
+      </c>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t>-36.88100357718987,175.05037706877366</t>
+        </is>
+      </c>
+      <c r="M392" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>-36.878989367524845,175.04223703554274</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>-36.879532492292235,175.0428410254875</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>-36.87995529019037,175.04357085683247</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>-36.88029273558773,175.0443460808578</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>-36.88064257433595,175.04513243571077</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>-36.8808295996123,175.0459790294262</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>-36.881002914262254,175.0468499536816</t>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>-36.88102941985196,175.04772003635017</t>
+        </is>
+      </c>
+      <c r="J393" t="inlineStr">
+        <is>
+          <t>-36.8810816000445,175.04861542915125</t>
+        </is>
+      </c>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>-36.88104819412665,175.0494992053841</t>
+        </is>
+      </c>
+      <c r="L393" t="inlineStr">
+        <is>
+          <t>-36.8810064999292,175.050377750449</t>
+        </is>
+      </c>
+      <c r="M393" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0602/nzd0602.xlsx
+++ b/data/nzd0602/nzd0602.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M393"/>
+  <dimension ref="A1:M395"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18135,6 +18135,96 @@
       <c r="M393" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B394" t="n">
+        <v>207.13</v>
+      </c>
+      <c r="C394" t="n">
+        <v>195.11</v>
+      </c>
+      <c r="D394" t="n">
+        <v>200.14</v>
+      </c>
+      <c r="E394" t="n">
+        <v>211.85</v>
+      </c>
+      <c r="F394" t="n">
+        <v>206.91</v>
+      </c>
+      <c r="G394" t="n">
+        <v>212.84</v>
+      </c>
+      <c r="H394" t="n">
+        <v>212.88</v>
+      </c>
+      <c r="I394" t="n">
+        <v>215.73</v>
+      </c>
+      <c r="J394" t="n">
+        <v>212.56</v>
+      </c>
+      <c r="K394" t="n">
+        <v>214.76</v>
+      </c>
+      <c r="L394" t="n">
+        <v>210.63</v>
+      </c>
+      <c r="M394" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:30+00:00</t>
+        </is>
+      </c>
+      <c r="B395" t="n">
+        <v>207.66</v>
+      </c>
+      <c r="C395" t="n">
+        <v>195.29</v>
+      </c>
+      <c r="D395" t="n">
+        <v>200.14</v>
+      </c>
+      <c r="E395" t="n">
+        <v>212.4</v>
+      </c>
+      <c r="F395" t="n">
+        <v>207.45</v>
+      </c>
+      <c r="G395" t="n">
+        <v>212.99</v>
+      </c>
+      <c r="H395" t="n">
+        <v>213.39</v>
+      </c>
+      <c r="I395" t="n">
+        <v>215.55</v>
+      </c>
+      <c r="J395" t="n">
+        <v>212.86</v>
+      </c>
+      <c r="K395" t="n">
+        <v>214.61</v>
+      </c>
+      <c r="L395" t="n">
+        <v>211.31</v>
+      </c>
+      <c r="M395" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -18149,7 +18239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B423"/>
+  <dimension ref="A1:B425"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22382,6 +22472,26 @@
       </c>
       <c r="B423" t="n">
         <v>0.43</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B424" t="n">
+        <v>-0.95</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B425" t="n">
+        <v>-0.95</v>
       </c>
     </row>
   </sheetData>
@@ -22544,28 +22654,28 @@
         <v>0.1008</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.007101249086859079</v>
+        <v>-0.0007910315525574238</v>
       </c>
       <c r="J2" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="K2" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="L2" t="n">
-        <v>0.000166547564556363</v>
+        <v>2.062032528282742e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>3.271313522953939</v>
+        <v>3.285338672965852</v>
       </c>
       <c r="N2" t="n">
-        <v>15.77787976782465</v>
+        <v>15.89875739118731</v>
       </c>
       <c r="O2" t="n">
-        <v>3.972137934138825</v>
+        <v>3.987324590648134</v>
       </c>
       <c r="P2" t="n">
-        <v>201.2502370382308</v>
+        <v>201.1785069707892</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22616,28 +22726,28 @@
         <v>0.0982</v>
       </c>
       <c r="I3" t="n">
-        <v>0.07704559605617409</v>
+        <v>0.08301594495715149</v>
       </c>
       <c r="J3" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="K3" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0289369534789794</v>
+        <v>0.03321741468221928</v>
       </c>
       <c r="M3" t="n">
-        <v>2.635197094557477</v>
+        <v>2.651561355095606</v>
       </c>
       <c r="N3" t="n">
-        <v>10.38197628850601</v>
+        <v>10.50891787405329</v>
       </c>
       <c r="O3" t="n">
-        <v>3.222107429696597</v>
+        <v>3.241746114990082</v>
       </c>
       <c r="P3" t="n">
-        <v>187.1451126938369</v>
+        <v>187.07724776185</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22688,28 +22798,28 @@
         <v>0.0887</v>
       </c>
       <c r="I4" t="n">
-        <v>0.006105822735555167</v>
+        <v>0.01291432864167832</v>
       </c>
       <c r="J4" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="K4" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0001750734338057391</v>
+        <v>0.0007744878828106483</v>
       </c>
       <c r="M4" t="n">
-        <v>2.641153481603148</v>
+        <v>2.663555750708623</v>
       </c>
       <c r="N4" t="n">
-        <v>11.09639392441174</v>
+        <v>11.27364955404819</v>
       </c>
       <c r="O4" t="n">
-        <v>3.3311250238338</v>
+        <v>3.357625582766516</v>
       </c>
       <c r="P4" t="n">
-        <v>193.1390747916059</v>
+        <v>193.0616836829045</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22760,28 +22870,28 @@
         <v>0.115</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.03244782917268845</v>
+        <v>-0.02729822613377509</v>
       </c>
       <c r="J5" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="K5" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004183135173913777</v>
+        <v>0.002964617670169756</v>
       </c>
       <c r="M5" t="n">
-        <v>2.902582621200208</v>
+        <v>2.917344578851496</v>
       </c>
       <c r="N5" t="n">
-        <v>13.06287119992319</v>
+        <v>13.13054365231313</v>
       </c>
       <c r="O5" t="n">
-        <v>3.61425942620659</v>
+        <v>3.623609202482123</v>
       </c>
       <c r="P5" t="n">
-        <v>207.8264025549225</v>
+        <v>207.7678648912513</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22832,28 +22942,28 @@
         <v>0.098</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1340078796300126</v>
+        <v>-0.1290491381088276</v>
       </c>
       <c r="J6" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="K6" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05184443332004873</v>
+        <v>0.04840171569093854</v>
       </c>
       <c r="M6" t="n">
-        <v>3.120471578016537</v>
+        <v>3.129194355965867</v>
       </c>
       <c r="N6" t="n">
-        <v>17.11701025382853</v>
+        <v>17.15438238445726</v>
       </c>
       <c r="O6" t="n">
-        <v>4.137270870251128</v>
+        <v>4.141784927354058</v>
       </c>
       <c r="P6" t="n">
-        <v>205.7854082886201</v>
+        <v>205.7290401179331</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -22904,28 +23014,28 @@
         <v>0.1269</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1559404103085435</v>
+        <v>-0.1479035550341156</v>
       </c>
       <c r="J7" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="K7" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08368856316305362</v>
+        <v>0.07501850616327188</v>
       </c>
       <c r="M7" t="n">
-        <v>3.11563036574475</v>
+        <v>3.139739490234619</v>
       </c>
       <c r="N7" t="n">
-        <v>13.87663334348247</v>
+        <v>14.13168127205788</v>
       </c>
       <c r="O7" t="n">
-        <v>3.725135345659601</v>
+        <v>3.759212852720351</v>
       </c>
       <c r="P7" t="n">
-        <v>209.0159845797809</v>
+        <v>208.9246301118581</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -22976,28 +23086,28 @@
         <v>0.1724</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.07525624520114552</v>
+        <v>-0.06934970586175272</v>
       </c>
       <c r="J8" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="K8" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0319814602016133</v>
+        <v>0.02704483736522179</v>
       </c>
       <c r="M8" t="n">
-        <v>2.422864551938335</v>
+        <v>2.439523464773703</v>
       </c>
       <c r="N8" t="n">
-        <v>8.934294231278228</v>
+        <v>9.065038969442904</v>
       </c>
       <c r="O8" t="n">
-        <v>2.98902897799239</v>
+        <v>3.010820315037565</v>
       </c>
       <c r="P8" t="n">
-        <v>209.2159265413962</v>
+        <v>209.1487851193439</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -23048,28 +23158,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2566666165774941</v>
+        <v>0.261971771754318</v>
       </c>
       <c r="J9" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="K9" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2115052235993591</v>
+        <v>0.2182841448147615</v>
       </c>
       <c r="M9" t="n">
-        <v>2.790100254837131</v>
+        <v>2.802097368709049</v>
       </c>
       <c r="N9" t="n">
-        <v>12.79989086301746</v>
+        <v>12.87679256231075</v>
       </c>
       <c r="O9" t="n">
-        <v>3.577693511610163</v>
+        <v>3.58842480237649</v>
       </c>
       <c r="P9" t="n">
-        <v>203.4517522436658</v>
+        <v>203.3914504736196</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -23120,28 +23230,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3672758248711815</v>
+        <v>0.3668059352059712</v>
       </c>
       <c r="J10" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="K10" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4243421659111853</v>
+        <v>0.4262134312051129</v>
       </c>
       <c r="M10" t="n">
-        <v>2.56803242843679</v>
+        <v>2.557142801941879</v>
       </c>
       <c r="N10" t="n">
-        <v>9.537239495663828</v>
+        <v>9.490037554937489</v>
       </c>
       <c r="O10" t="n">
-        <v>3.088242136825386</v>
+        <v>3.080590455568135</v>
       </c>
       <c r="P10" t="n">
-        <v>203.3595585661643</v>
+        <v>203.3648982319077</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -23192,28 +23302,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4040760918189107</v>
+        <v>0.4050853944091348</v>
       </c>
       <c r="J11" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="K11" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5392262294349209</v>
+        <v>0.5428562853782513</v>
       </c>
       <c r="M11" t="n">
-        <v>2.030887823404288</v>
+        <v>2.025293849771733</v>
       </c>
       <c r="N11" t="n">
-        <v>7.271647573920106</v>
+        <v>7.23990766950026</v>
       </c>
       <c r="O11" t="n">
-        <v>2.696599260906245</v>
+        <v>2.690707652180047</v>
       </c>
       <c r="P11" t="n">
-        <v>202.8622488265618</v>
+        <v>202.8507771780187</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -23264,28 +23374,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3389256616325262</v>
+        <v>0.337319351053137</v>
       </c>
       <c r="J12" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="K12" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3924223669866008</v>
+        <v>0.3922728137241513</v>
       </c>
       <c r="M12" t="n">
-        <v>2.334005154729851</v>
+        <v>2.329038078955157</v>
       </c>
       <c r="N12" t="n">
-        <v>9.269294960197398</v>
+        <v>9.235808984832998</v>
       </c>
       <c r="O12" t="n">
-        <v>3.044551684599458</v>
+        <v>3.039047381143143</v>
       </c>
       <c r="P12" t="n">
-        <v>203.5208278885988</v>
+        <v>203.5390829799525</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -23323,7 +23433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M393"/>
+  <dimension ref="A1:M395"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49657,6 +49767,140 @@
         </is>
       </c>
     </row>
+    <row r="394">
+      <c r="A394" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>-36.878970808656504,175.04225644445154</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>-36.87951752093391,175.04285668247314</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>-36.87994659708953,175.04357994794861</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>-36.88026966143146,175.04435985739562</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>-36.88062136878363,175.04514509637497</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>-36.88080947536527,175.04598519658174</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>-36.88098103520467,175.0468566323792</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>-36.88101348517883,175.04772088686607</t>
+        </is>
+      </c>
+      <c r="J394" t="inlineStr">
+        <is>
+          <t>-36.881072777456794,175.04861589995514</t>
+        </is>
+      </c>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>-36.8810288443256,175.0494980142198</t>
+        </is>
+      </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>-36.88099480897186,175.05037502374807</t>
+        </is>
+      </c>
+      <c r="M394" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:30+00:00</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>-36.87896715207615,175.04226026851052</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>-36.87951627907,175.042857981209</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>-36.87994659708953,175.04357994794861</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>-36.88026519284468,175.04436252538616</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>-36.88061698142782,175.04514771582186</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>-36.88080816291435,175.04598559878744</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>-36.88097657187689,175.04685799483306</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>-36.88101510565407,175.04772080037293</t>
+        </is>
+      </c>
+      <c r="J395" t="inlineStr">
+        <is>
+          <t>-36.88107007666465,175.04861604407878</t>
+        </is>
+      </c>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>-36.881030194311705,175.04949809732426</t>
+        </is>
+      </c>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>-36.880988786357435,175.05037361908433</t>
+        </is>
+      </c>
+      <c r="M395" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
